--- a/fuction_ensemble/redes-ensemble-s/Teste03/content/results/metrics_9_8.xlsx
+++ b/fuction_ensemble/redes-ensemble-s/Teste03/content/results/metrics_9_8.xlsx
@@ -513,661 +513,661 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>model_9_8_24</t>
+          <t>model_9_8_0</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9993790413247443</v>
+        <v>0.9998145407328221</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5826960450156655</v>
+        <v>0.6618298626895199</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9984249596186953</v>
+        <v>0.9999999999997585</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9876687042454408</v>
+        <v>0.9999999999997243</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9959031546152111</v>
+        <v>0.9999999999998143</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0003686278936498416</v>
+        <v>0.0001100966324200179</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2477296542709265</v>
+        <v>0.2007524016967964</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0003393585426663299</v>
+        <v>1.089072256656613e-13</v>
       </c>
       <c r="J2" t="n">
-        <v>0.001942403418240276</v>
+        <v>1.135344139075531e-13</v>
       </c>
       <c r="K2" t="n">
-        <v>0.001140880980453303</v>
+        <v>1.441145369649501e-13</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004426106764659802</v>
+        <v>0.002101715004940108</v>
       </c>
       <c r="M2" t="n">
-        <v>0.01919968472787617</v>
+        <v>0.01049269424028061</v>
       </c>
       <c r="N2" t="n">
-        <v>1.000244311609937</v>
+        <v>1.000072967580529</v>
       </c>
       <c r="O2" t="n">
-        <v>0.02001705505556834</v>
+        <v>0.01093938995696077</v>
       </c>
       <c r="P2" t="n">
-        <v>185.8114456820253</v>
+        <v>188.2283042025219</v>
       </c>
       <c r="Q2" t="n">
-        <v>289.4158907958224</v>
+        <v>291.8327493163189</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>model_9_8_23</t>
+          <t>model_9_8_22</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9993805680167613</v>
+        <v>0.9998145407328221</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5826752134022739</v>
+        <v>0.6618298626895199</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9984593244417652</v>
+        <v>0.9999999999997585</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9876906793175262</v>
+        <v>0.9999999999997243</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9959226575987421</v>
+        <v>0.9999999999998143</v>
       </c>
       <c r="G3" t="n">
-        <v>0.000367721583318888</v>
+        <v>0.0001100966324200179</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2477420208165146</v>
+        <v>0.2007524016967964</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0003319542904233977</v>
+        <v>1.089072256656613e-13</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001938941944605691</v>
+        <v>1.135344139075531e-13</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001135449830169898</v>
+        <v>1.441145369649501e-13</v>
       </c>
       <c r="L3" t="n">
-        <v>0.004482202523016138</v>
+        <v>0.002101715004940108</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01917606798378875</v>
+        <v>0.01049269424028061</v>
       </c>
       <c r="N3" t="n">
-        <v>1.000243710944225</v>
+        <v>1.000072967580529</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01999243289779171</v>
+        <v>0.01093938995696077</v>
       </c>
       <c r="P3" t="n">
-        <v>185.8163689464098</v>
+        <v>188.2283042025219</v>
       </c>
       <c r="Q3" t="n">
-        <v>289.4208140602068</v>
+        <v>291.8327493163189</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>model_9_8_22</t>
+          <t>model_9_8_21</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9993820071267503</v>
+        <v>0.9998145407328221</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5826510270421261</v>
+        <v>0.6618298626895199</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9984967876271432</v>
+        <v>0.9999999999997585</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9877141070107369</v>
+        <v>0.9999999999997243</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9959437853620179</v>
+        <v>0.9999999999998143</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0003668672654631123</v>
+        <v>0.0001100966324200179</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2477563788846947</v>
+        <v>0.2007524016967964</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0003238824643645669</v>
+        <v>1.089072256656613e-13</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001935251656717073</v>
+        <v>1.135344139075531e-13</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001129566214603054</v>
+        <v>1.441145369649501e-13</v>
       </c>
       <c r="L4" t="n">
-        <v>0.004544843648459635</v>
+        <v>0.002101715004940108</v>
       </c>
       <c r="M4" t="n">
-        <v>0.01915377940415709</v>
+        <v>0.01049269424028061</v>
       </c>
       <c r="N4" t="n">
-        <v>1.000243144737016</v>
+        <v>1.000072967580529</v>
       </c>
       <c r="O4" t="n">
-        <v>0.01996919544718141</v>
+        <v>0.01093938995696077</v>
       </c>
       <c r="P4" t="n">
-        <v>185.8210208996342</v>
+        <v>188.2283042025219</v>
       </c>
       <c r="Q4" t="n">
-        <v>289.4254660134313</v>
+        <v>291.8327493163189</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>model_9_8_21</t>
+          <t>model_9_8_20</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9993832859113352</v>
+        <v>0.9998145407328221</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5826230998477342</v>
+        <v>0.6618298626895199</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9985375163502437</v>
+        <v>0.9999999999997585</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9877388576713797</v>
+        <v>0.9999999999997243</v>
       </c>
       <c r="F5" t="n">
-        <v>0.995966538345427</v>
+        <v>0.9999999999998143</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0003661081236928914</v>
+        <v>0.0001100966324200179</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2477729576736778</v>
+        <v>0.2007524016967964</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0003151070448387526</v>
+        <v>1.089072256656613e-13</v>
       </c>
       <c r="J5" t="n">
-        <v>0.00193135297738983</v>
+        <v>1.135344139075531e-13</v>
       </c>
       <c r="K5" t="n">
-        <v>0.001123230011114292</v>
+        <v>1.441145369649501e-13</v>
       </c>
       <c r="L5" t="n">
-        <v>0.004614402560502972</v>
+        <v>0.002101715004940108</v>
       </c>
       <c r="M5" t="n">
-        <v>0.01913395211901847</v>
+        <v>0.01049269424028061</v>
       </c>
       <c r="N5" t="n">
-        <v>1.000242641608655</v>
+        <v>1.000072967580529</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0199485240734663</v>
+        <v>0.01093938995696077</v>
       </c>
       <c r="P5" t="n">
-        <v>185.8251636965297</v>
+        <v>188.2283042025219</v>
       </c>
       <c r="Q5" t="n">
-        <v>289.4296088103267</v>
+        <v>291.8327493163189</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>model_9_8_20</t>
+          <t>model_9_8_19</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9993843217275789</v>
+        <v>0.9998145407328221</v>
       </c>
       <c r="C6" t="n">
-        <v>0.5825907444577312</v>
+        <v>0.6618298626895199</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9985817510835863</v>
+        <v>0.9999999999997585</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9877649195398175</v>
+        <v>0.9999999999997243</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9959910156220074</v>
+        <v>0.9999999999998143</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0003654932184257106</v>
+        <v>0.0001100966324200179</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2477921652308636</v>
+        <v>0.2007524016967964</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0003055762195846606</v>
+        <v>1.089072256656613e-13</v>
       </c>
       <c r="J6" t="n">
-        <v>0.001927247758980774</v>
+        <v>1.135344139075531e-13</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001116413630050094</v>
+        <v>1.441145369649501e-13</v>
       </c>
       <c r="L6" t="n">
-        <v>0.004693657176615172</v>
+        <v>0.002101715004940108</v>
       </c>
       <c r="M6" t="n">
-        <v>0.01911787693300986</v>
+        <v>0.01049269424028061</v>
       </c>
       <c r="N6" t="n">
-        <v>1.000242234074395</v>
+        <v>1.000072967580529</v>
       </c>
       <c r="O6" t="n">
-        <v>0.01993176453350909</v>
+        <v>0.01093938995696077</v>
       </c>
       <c r="P6" t="n">
-        <v>185.8285256663708</v>
+        <v>188.2283042025219</v>
       </c>
       <c r="Q6" t="n">
-        <v>289.4329707801679</v>
+        <v>291.8327493163189</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>model_9_8_19</t>
+          <t>model_9_8_18</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.999384996919804</v>
+        <v>0.9998145407328221</v>
       </c>
       <c r="C7" t="n">
-        <v>0.5825531612506226</v>
+        <v>0.6618298626895199</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9986295840332309</v>
+        <v>0.9999999999997585</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9877921731913367</v>
+        <v>0.9999999999997243</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9960172366252689</v>
+        <v>0.9999999999998143</v>
       </c>
       <c r="G7" t="n">
-        <v>0.000365092395154127</v>
+        <v>0.0001100966324200179</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2478144762461132</v>
+        <v>0.2007524016967964</v>
       </c>
       <c r="I7" t="n">
-        <v>0.00029527012186457</v>
+        <v>1.089072256656613e-13</v>
       </c>
       <c r="J7" t="n">
-        <v>0.001922954813054882</v>
+        <v>1.135344139075531e-13</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001109111659607051</v>
+        <v>1.441145369649501e-13</v>
       </c>
       <c r="L7" t="n">
-        <v>0.004785277738183203</v>
+        <v>0.002101715004940108</v>
       </c>
       <c r="M7" t="n">
-        <v>0.01910739111323487</v>
+        <v>0.01049269424028061</v>
       </c>
       <c r="N7" t="n">
-        <v>1.000241968424995</v>
+        <v>1.000072967580529</v>
       </c>
       <c r="O7" t="n">
-        <v>0.01992083231067764</v>
+        <v>0.01093938995696077</v>
       </c>
       <c r="P7" t="n">
-        <v>185.8307201980142</v>
+        <v>188.2283042025219</v>
       </c>
       <c r="Q7" t="n">
-        <v>289.4351653118112</v>
+        <v>291.8327493163189</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>model_9_8_18</t>
+          <t>model_9_8_17</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.999385170592001</v>
+        <v>0.9998145407328221</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5825094602246333</v>
+        <v>0.6618298626895199</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9986812079648779</v>
+        <v>0.9999999999997585</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9878204548533541</v>
+        <v>0.9999999999997243</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9960452032305094</v>
+        <v>0.9999999999998143</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0003649892958357092</v>
+        <v>0.0001100966324200179</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2478404190629265</v>
+        <v>0.2007524016967964</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0002841472183387795</v>
+        <v>1.089072256656613e-13</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001918499936773471</v>
+        <v>1.135344139075531e-13</v>
       </c>
       <c r="K8" t="n">
-        <v>0.001101323577556125</v>
+        <v>1.441145369649501e-13</v>
       </c>
       <c r="L8" t="n">
-        <v>0.004887037438035875</v>
+        <v>0.002101715004940108</v>
       </c>
       <c r="M8" t="n">
-        <v>0.01910469303170583</v>
+        <v>0.01049269424028061</v>
       </c>
       <c r="N8" t="n">
-        <v>1.000241900094951</v>
+        <v>1.000072967580529</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0199180193662321</v>
+        <v>0.01093938995696077</v>
       </c>
       <c r="P8" t="n">
-        <v>185.8312850625786</v>
+        <v>188.2283042025219</v>
       </c>
       <c r="Q8" t="n">
-        <v>289.4357301763757</v>
+        <v>291.8327493163189</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>model_9_8_17</t>
+          <t>model_9_8_16</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9993846428014829</v>
+        <v>0.9998145407328221</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5824585325647829</v>
+        <v>0.6618298626895199</v>
       </c>
       <c r="D9" t="n">
-        <v>0.998736720301414</v>
+        <v>0.9999999999997585</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9878491936959957</v>
+        <v>0.9999999999997243</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9960748090635206</v>
+        <v>0.9999999999998143</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0003653026150866705</v>
+        <v>0.0001100966324200179</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2478706519217742</v>
+        <v>0.2007524016967964</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0002721865182510338</v>
+        <v>1.089072256656613e-13</v>
       </c>
       <c r="J9" t="n">
-        <v>0.001913973046226486</v>
+        <v>1.135344139075531e-13</v>
       </c>
       <c r="K9" t="n">
-        <v>0.001093079006765518</v>
+        <v>1.441145369649501e-13</v>
       </c>
       <c r="L9" t="n">
-        <v>0.005000172001144122</v>
+        <v>0.002101715004940108</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01911289133246643</v>
+        <v>0.01049269424028061</v>
       </c>
       <c r="N9" t="n">
-        <v>1.000242107750236</v>
+        <v>1.000072967580529</v>
       </c>
       <c r="O9" t="n">
-        <v>0.01992656668562891</v>
+        <v>0.01093938995696077</v>
       </c>
       <c r="P9" t="n">
-        <v>185.8295689309031</v>
+        <v>188.2283042025219</v>
       </c>
       <c r="Q9" t="n">
-        <v>289.4340140447001</v>
+        <v>291.8327493163189</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>model_9_8_16</t>
+          <t>model_9_8_15</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9993831952665505</v>
+        <v>0.9998145407328221</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5823992631835408</v>
+        <v>0.6618298626895199</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9987962627061681</v>
+        <v>0.9999999999997585</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9878782410999668</v>
+        <v>0.9999999999997243</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9961060530682172</v>
+        <v>0.9999999999998143</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0003661619343527527</v>
+        <v>0.0001100966324200179</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2479058367867834</v>
+        <v>0.2007524016967964</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0002593574987896769</v>
+        <v>1.089072256656613e-13</v>
       </c>
       <c r="J10" t="n">
-        <v>0.001909397551656622</v>
+        <v>1.135344139075531e-13</v>
       </c>
       <c r="K10" t="n">
-        <v>0.00108437824133173</v>
+        <v>1.441145369649501e-13</v>
       </c>
       <c r="L10" t="n">
-        <v>0.005125765699036865</v>
+        <v>0.002101715004940108</v>
       </c>
       <c r="M10" t="n">
-        <v>0.01913535822378961</v>
+        <v>0.01049269424028061</v>
       </c>
       <c r="N10" t="n">
-        <v>1.000242677272177</v>
+        <v>1.000072967580529</v>
       </c>
       <c r="O10" t="n">
-        <v>0.01994999003902859</v>
+        <v>0.01093938995696077</v>
       </c>
       <c r="P10" t="n">
-        <v>185.8248697576509</v>
+        <v>188.2283042025219</v>
       </c>
       <c r="Q10" t="n">
-        <v>289.429314871448</v>
+        <v>291.8327493163189</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>model_9_8_15</t>
+          <t>model_9_8_14</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9993805141375788</v>
+        <v>0.9998145407328221</v>
       </c>
       <c r="C11" t="n">
-        <v>0.582330208371835</v>
+        <v>0.6618298626895199</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9988597886491505</v>
+        <v>0.9999999999997585</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9879067923096387</v>
+        <v>0.9999999999997243</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9961387055277948</v>
+        <v>0.9999999999998143</v>
       </c>
       <c r="G11" t="n">
-        <v>0.000367753568329121</v>
+        <v>0.0001100966324200179</v>
       </c>
       <c r="H11" t="n">
-        <v>0.2479468307060244</v>
+        <v>0.2007524016967964</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0002456701853163845</v>
+        <v>1.089072256656613e-13</v>
       </c>
       <c r="J11" t="n">
-        <v>0.001904900216715872</v>
+        <v>1.135344139075531e-13</v>
       </c>
       <c r="K11" t="n">
-        <v>0.001075285252312577</v>
+        <v>1.441145369649501e-13</v>
       </c>
       <c r="L11" t="n">
-        <v>0.005265324411892111</v>
+        <v>0.002101715004940108</v>
       </c>
       <c r="M11" t="n">
-        <v>0.01917690194815421</v>
+        <v>0.01049269424028061</v>
       </c>
       <c r="N11" t="n">
-        <v>1.000243732142592</v>
+        <v>1.000072967580529</v>
       </c>
       <c r="O11" t="n">
-        <v>0.01999330236574676</v>
+        <v>0.01093938995696077</v>
       </c>
       <c r="P11" t="n">
-        <v>185.8161949907829</v>
+        <v>188.2283042025219</v>
       </c>
       <c r="Q11" t="n">
-        <v>289.42064010458</v>
+        <v>291.8327493163189</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>model_9_8_14</t>
+          <t>model_9_8_13</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9993762652374362</v>
+        <v>0.9998145407328221</v>
       </c>
       <c r="C12" t="n">
-        <v>0.5822497256316899</v>
+        <v>0.6618298626895199</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9989273291248686</v>
+        <v>0.9999999999997585</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9879348923369295</v>
+        <v>0.9999999999997243</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9961727814395865</v>
+        <v>0.9999999999998143</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0003702758989966649</v>
+        <v>0.0001100966324200179</v>
       </c>
       <c r="H12" t="n">
-        <v>0.247994608737248</v>
+        <v>0.2007524016967964</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0002311178997478587</v>
+        <v>1.089072256656613e-13</v>
       </c>
       <c r="J12" t="n">
-        <v>0.001900473951208269</v>
+        <v>1.135344139075531e-13</v>
       </c>
       <c r="K12" t="n">
-        <v>0.001065795863281889</v>
+        <v>1.441145369649501e-13</v>
       </c>
       <c r="L12" t="n">
-        <v>0.005420328308811783</v>
+        <v>0.002101715004940108</v>
       </c>
       <c r="M12" t="n">
-        <v>0.01924255437816573</v>
+        <v>0.01049269424028061</v>
       </c>
       <c r="N12" t="n">
-        <v>1.000245403841009</v>
+        <v>1.000072967580529</v>
       </c>
       <c r="O12" t="n">
-        <v>0.02006174975562312</v>
+        <v>0.01093938995696077</v>
       </c>
       <c r="P12" t="n">
-        <v>185.802524314476</v>
+        <v>188.2283042025219</v>
       </c>
       <c r="Q12" t="n">
-        <v>289.406969428273</v>
+        <v>291.8327493163189</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>model_9_8_13</t>
+          <t>model_9_8_23</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9993699623988551</v>
+        <v>0.9998145407328221</v>
       </c>
       <c r="C13" t="n">
-        <v>0.5821558767866424</v>
+        <v>0.6618298626895199</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9989987326563669</v>
+        <v>0.9999999999997585</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9879612044939116</v>
+        <v>0.9999999999997243</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9962078427744218</v>
+        <v>0.9999999999998143</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0003740175362468476</v>
+        <v>0.0001100966324200179</v>
       </c>
       <c r="H13" t="n">
-        <v>0.2480503214657272</v>
+        <v>0.2007524016967964</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0002157332793418711</v>
+        <v>1.089072256656613e-13</v>
       </c>
       <c r="J13" t="n">
-        <v>0.001896329307800116</v>
+        <v>1.135344139075531e-13</v>
       </c>
       <c r="K13" t="n">
-        <v>0.001056032055691954</v>
+        <v>1.441145369649501e-13</v>
       </c>
       <c r="L13" t="n">
-        <v>0.005592580411640208</v>
+        <v>0.002101715004940108</v>
       </c>
       <c r="M13" t="n">
-        <v>0.01933953298936786</v>
+        <v>0.01049269424028061</v>
       </c>
       <c r="N13" t="n">
-        <v>1.000247883646352</v>
+        <v>1.000072967580529</v>
       </c>
       <c r="O13" t="n">
-        <v>0.02016285694707753</v>
+        <v>0.01093938995696077</v>
       </c>
       <c r="P13" t="n">
-        <v>185.7824157465768</v>
+        <v>188.2283042025219</v>
       </c>
       <c r="Q13" t="n">
-        <v>289.3868608603739</v>
+        <v>291.8327493163189</v>
       </c>
     </row>
     <row r="14">
@@ -1177,712 +1177,712 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9993610670133944</v>
+        <v>0.9998145407328221</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5820464816405897</v>
+        <v>0.6618298626895199</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9990738806131311</v>
+        <v>0.9999999999997585</v>
       </c>
       <c r="E14" t="n">
-        <v>0.987985367033493</v>
+        <v>0.9999999999997243</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9962437503948623</v>
+        <v>0.9999999999998143</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0003792982213169281</v>
+        <v>0.0001100966324200179</v>
       </c>
       <c r="H14" t="n">
-        <v>0.2481152631500483</v>
+        <v>0.2007524016967964</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0001995418842547658</v>
+        <v>1.089072256656613e-13</v>
       </c>
       <c r="J14" t="n">
-        <v>0.001892523268239428</v>
+        <v>1.135344139075531e-13</v>
       </c>
       <c r="K14" t="n">
-        <v>0.001046032576247097</v>
+        <v>1.441145369649501e-13</v>
       </c>
       <c r="L14" t="n">
-        <v>0.005783840796141348</v>
+        <v>0.002101715004940108</v>
       </c>
       <c r="M14" t="n">
-        <v>0.01947558012786598</v>
+        <v>0.01049269424028061</v>
       </c>
       <c r="N14" t="n">
-        <v>1.00025138347014</v>
+        <v>1.000072967580529</v>
       </c>
       <c r="O14" t="n">
-        <v>0.02030469589391792</v>
+        <v>0.01093938995696077</v>
       </c>
       <c r="P14" t="n">
-        <v>185.7543755973274</v>
+        <v>188.2283042025219</v>
       </c>
       <c r="Q14" t="n">
-        <v>289.3588207111244</v>
+        <v>291.8327493163189</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>model_9_8_11</t>
+          <t>model_9_8_10</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9993488596938266</v>
+        <v>0.9998145407328221</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5819192483087338</v>
+        <v>0.6618298626895199</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9991524102403918</v>
+        <v>0.9999999999997585</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9880060918892858</v>
+        <v>0.9999999999997243</v>
       </c>
       <c r="F15" t="n">
-        <v>0.996279991243663</v>
+        <v>0.9999999999998143</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0003865450135412031</v>
+        <v>0.0001100966324200179</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2481907943520317</v>
+        <v>0.2007524016967964</v>
       </c>
       <c r="I15" t="n">
-        <v>0.000182621873707937</v>
+        <v>1.089072256656613e-13</v>
       </c>
       <c r="J15" t="n">
-        <v>0.001889258726415477</v>
+        <v>1.135344139075531e-13</v>
       </c>
       <c r="K15" t="n">
-        <v>0.001035940300061707</v>
+        <v>1.441145369649501e-13</v>
       </c>
       <c r="L15" t="n">
-        <v>0.005996502872644633</v>
+        <v>0.002101715004940108</v>
       </c>
       <c r="M15" t="n">
-        <v>0.01966074804124205</v>
+        <v>0.01049269424028061</v>
       </c>
       <c r="N15" t="n">
-        <v>1.00025618634997</v>
+        <v>1.000072967580529</v>
       </c>
       <c r="O15" t="n">
-        <v>0.02049774678871683</v>
+        <v>0.01093938995696077</v>
       </c>
       <c r="P15" t="n">
-        <v>185.7165244643747</v>
+        <v>188.2283042025219</v>
       </c>
       <c r="Q15" t="n">
-        <v>289.3209695781717</v>
+        <v>291.8327493163189</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>model_9_8_10</t>
+          <t>model_9_8_9</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.999332495730642</v>
+        <v>0.9998145407328221</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5817715288292689</v>
+        <v>0.6618298626895199</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9992339580599617</v>
+        <v>0.9999999999997585</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9880225338965808</v>
+        <v>0.9999999999997243</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9963161884154217</v>
+        <v>0.9999999999998143</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0003962593689739438</v>
+        <v>0.0001100966324200179</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2482784870161914</v>
+        <v>0.2007524016967964</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0001650515627906128</v>
+        <v>1.089072256656613e-13</v>
       </c>
       <c r="J16" t="n">
-        <v>0.001886668811145552</v>
+        <v>1.135344139075531e-13</v>
       </c>
       <c r="K16" t="n">
-        <v>0.001025860186968082</v>
+        <v>1.441145369649501e-13</v>
       </c>
       <c r="L16" t="n">
-        <v>0.006232769519497072</v>
+        <v>0.002101715004940108</v>
       </c>
       <c r="M16" t="n">
-        <v>0.01990626456605919</v>
+        <v>0.01049269424028061</v>
       </c>
       <c r="N16" t="n">
-        <v>1.000262624630567</v>
+        <v>1.000072967580529</v>
       </c>
       <c r="O16" t="n">
-        <v>0.02075371546028471</v>
+        <v>0.01093938995696077</v>
       </c>
       <c r="P16" t="n">
-        <v>185.666883177908</v>
+        <v>188.2283042025219</v>
       </c>
       <c r="Q16" t="n">
-        <v>289.2713282917051</v>
+        <v>291.8327493163189</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>model_9_8_9</t>
+          <t>model_9_8_8</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9993109077048038</v>
+        <v>0.9998145407328221</v>
       </c>
       <c r="C17" t="n">
-        <v>0.5816003129496872</v>
+        <v>0.6618298626895199</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9993179698789794</v>
+        <v>0.9999999999997585</v>
       </c>
       <c r="E17" t="n">
-        <v>0.988033473836689</v>
+        <v>0.9999999999997243</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9963517826994861</v>
+        <v>0.9999999999998143</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0004090749536656441</v>
+        <v>0.0001100966324200179</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2483801281584519</v>
+        <v>0.2007524016967964</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0001469503580171037</v>
+        <v>1.089072256656613e-13</v>
       </c>
       <c r="J17" t="n">
-        <v>0.00188494557155383</v>
+        <v>1.135344139075531e-13</v>
       </c>
       <c r="K17" t="n">
-        <v>0.001015947964785467</v>
+        <v>1.441145369649501e-13</v>
       </c>
       <c r="L17" t="n">
-        <v>0.006495424946248884</v>
+        <v>0.002101715004940108</v>
       </c>
       <c r="M17" t="n">
-        <v>0.02022560144138226</v>
+        <v>0.01049269424028061</v>
       </c>
       <c r="N17" t="n">
-        <v>1.000271118280077</v>
+        <v>1.000072967580529</v>
       </c>
       <c r="O17" t="n">
-        <v>0.02108664716750874</v>
+        <v>0.01093938995696077</v>
       </c>
       <c r="P17" t="n">
-        <v>185.603224315831</v>
+        <v>188.2283042025219</v>
       </c>
       <c r="Q17" t="n">
-        <v>289.207669429628</v>
+        <v>291.8327493163189</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>model_9_8_8</t>
+          <t>model_9_8_7</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9992828000871591</v>
+        <v>0.9998145407328221</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5814026361284633</v>
+        <v>0.6618298626895199</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9994037734410574</v>
+        <v>0.9999999999997585</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9880377542477905</v>
+        <v>0.9999999999997243</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9963861900209738</v>
+        <v>0.9999999999998143</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0004257608496854063</v>
+        <v>0.0001100966324200179</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2484974776587244</v>
+        <v>0.2007524016967964</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0001284631038945927</v>
+        <v>1.089072256656613e-13</v>
       </c>
       <c r="J18" t="n">
-        <v>0.001884271328934045</v>
+        <v>1.135344139075531e-13</v>
       </c>
       <c r="K18" t="n">
-        <v>0.00100636628547203</v>
+        <v>1.441145369649501e-13</v>
       </c>
       <c r="L18" t="n">
-        <v>0.006787469038805092</v>
+        <v>0.002101715004940108</v>
       </c>
       <c r="M18" t="n">
-        <v>0.02063397319193292</v>
+        <v>0.01049269424028061</v>
       </c>
       <c r="N18" t="n">
-        <v>1.000282177014888</v>
+        <v>1.000072967580529</v>
       </c>
       <c r="O18" t="n">
-        <v>0.0215124041489264</v>
+        <v>0.01093938995696077</v>
       </c>
       <c r="P18" t="n">
-        <v>185.5232655100917</v>
+        <v>188.2283042025219</v>
       </c>
       <c r="Q18" t="n">
-        <v>289.1277106238888</v>
+        <v>291.8327493163189</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>model_9_8_7</t>
+          <t>model_9_8_6</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9992465726676262</v>
+        <v>0.9998145407328221</v>
       </c>
       <c r="C19" t="n">
-        <v>0.5811751230322055</v>
+        <v>0.6618298626895199</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9994904728485413</v>
+        <v>0.9999999999997585</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9880342944387901</v>
+        <v>0.9999999999997243</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9964187503178059</v>
+        <v>0.9999999999998143</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0004472670108631895</v>
+        <v>0.0001100966324200179</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2486325392607171</v>
+        <v>0.2007524016967964</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0001097828307263466</v>
+        <v>1.089072256656613e-13</v>
       </c>
       <c r="J19" t="n">
-        <v>0.001884816311794126</v>
+        <v>1.135344139075531e-13</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0009972989617425393</v>
+        <v>1.441145369649501e-13</v>
       </c>
       <c r="L19" t="n">
-        <v>0.007112420493530137</v>
+        <v>0.002101715004940108</v>
       </c>
       <c r="M19" t="n">
-        <v>0.02114868815939158</v>
+        <v>0.01049269424028061</v>
       </c>
       <c r="N19" t="n">
-        <v>1.000296430425852</v>
+        <v>1.000072967580529</v>
       </c>
       <c r="O19" t="n">
-        <v>0.02204903159815665</v>
+        <v>0.01093938995696077</v>
       </c>
       <c r="P19" t="n">
-        <v>185.4247096038968</v>
+        <v>188.2283042025219</v>
       </c>
       <c r="Q19" t="n">
-        <v>289.0291547176938</v>
+        <v>291.8327493163189</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>model_9_8_6</t>
+          <t>model_9_8_5</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9992002814293641</v>
+        <v>0.9998145407328221</v>
       </c>
       <c r="C20" t="n">
-        <v>0.580914316293258</v>
+        <v>0.6618298626895199</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9995769678903943</v>
+        <v>0.9999999999997585</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9880220759637356</v>
+        <v>0.9999999999997243</v>
       </c>
       <c r="F20" t="n">
-        <v>0.996448756545391</v>
+        <v>0.9999999999998143</v>
       </c>
       <c r="G20" t="n">
-        <v>0.000474747489572917</v>
+        <v>0.0001100966324200179</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2487873654072209</v>
+        <v>0.2007524016967964</v>
       </c>
       <c r="I20" t="n">
-        <v>9.114659022133749e-05</v>
+        <v>1.089072256656613e-13</v>
       </c>
       <c r="J20" t="n">
-        <v>0.001886740943899611</v>
+        <v>1.135344139075531e-13</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0009889428899039019</v>
+        <v>1.441145369649501e-13</v>
       </c>
       <c r="L20" t="n">
-        <v>0.00747365214190253</v>
+        <v>0.002101715004940108</v>
       </c>
       <c r="M20" t="n">
-        <v>0.02178870096111553</v>
+        <v>0.01049269424028061</v>
       </c>
       <c r="N20" t="n">
-        <v>1.000314643372054</v>
+        <v>1.000072967580529</v>
       </c>
       <c r="O20" t="n">
-        <v>0.02271629106985914</v>
+        <v>0.01093938995696077</v>
       </c>
       <c r="P20" t="n">
-        <v>185.3054549923572</v>
+        <v>188.2283042025219</v>
       </c>
       <c r="Q20" t="n">
-        <v>288.9099001061543</v>
+        <v>291.8327493163189</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>model_9_8_5</t>
+          <t>model_9_8_4</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.999141502335319</v>
+        <v>0.9998145407328221</v>
       </c>
       <c r="C21" t="n">
-        <v>0.5806170998226512</v>
+        <v>0.6618298626895199</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9996619018216635</v>
+        <v>0.9999999999997585</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9879997307563675</v>
+        <v>0.9999999999997243</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9964752879031611</v>
+        <v>0.9999999999998143</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0005096412989227801</v>
+        <v>0.0001100966324200179</v>
       </c>
       <c r="H21" t="n">
-        <v>0.248963805943256</v>
+        <v>0.2007524016967964</v>
       </c>
       <c r="I21" t="n">
-        <v>7.284670694181074e-05</v>
+        <v>1.089072256656613e-13</v>
       </c>
       <c r="J21" t="n">
-        <v>0.001890260720574904</v>
+        <v>1.135344139075531e-13</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0009815544925829206</v>
+        <v>1.441145369649501e-13</v>
       </c>
       <c r="L21" t="n">
-        <v>0.007875811136746369</v>
+        <v>0.002101715004940108</v>
       </c>
       <c r="M21" t="n">
-        <v>0.02257523640901198</v>
+        <v>0.01049269424028061</v>
       </c>
       <c r="N21" t="n">
-        <v>1.000337769572989</v>
+        <v>1.000072967580529</v>
       </c>
       <c r="O21" t="n">
-        <v>0.02353631096012537</v>
+        <v>0.01093938995696077</v>
       </c>
       <c r="P21" t="n">
-        <v>185.1636068302957</v>
+        <v>188.2283042025219</v>
       </c>
       <c r="Q21" t="n">
-        <v>288.7680519440927</v>
+        <v>291.8327493163189</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>model_9_8_4</t>
+          <t>model_9_8_3</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9990672772186776</v>
+        <v>0.9998145407328221</v>
       </c>
       <c r="C22" t="n">
-        <v>0.5802801706651319</v>
+        <v>0.6618298626895199</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9997434795601865</v>
+        <v>0.9999999999997585</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9879669107582588</v>
+        <v>0.9999999999997243</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9964975671706531</v>
+        <v>0.9999999999998143</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0005537045345191612</v>
+        <v>0.0001100966324200179</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2491638216457412</v>
+        <v>0.2007524016967964</v>
       </c>
       <c r="I22" t="n">
-        <v>5.52699496803505e-05</v>
+        <v>1.089072256656613e-13</v>
       </c>
       <c r="J22" t="n">
-        <v>0.001895430467354303</v>
+        <v>1.135344139075531e-13</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0009753502085173266</v>
+        <v>1.441145369649501e-13</v>
       </c>
       <c r="L22" t="n">
-        <v>0.008323625450312521</v>
+        <v>0.002101715004940108</v>
       </c>
       <c r="M22" t="n">
-        <v>0.02353092719208406</v>
+        <v>0.01049269424028061</v>
       </c>
       <c r="N22" t="n">
-        <v>1.000366972897569</v>
+        <v>1.000072967580529</v>
       </c>
       <c r="O22" t="n">
-        <v>0.02453268747838548</v>
+        <v>0.01093938995696077</v>
       </c>
       <c r="P22" t="n">
-        <v>184.997758689363</v>
+        <v>188.2283042025219</v>
       </c>
       <c r="Q22" t="n">
-        <v>288.6022038031601</v>
+        <v>291.8327493163189</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>model_9_8_3</t>
+          <t>model_9_8_2</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9989739589878155</v>
+        <v>0.9998145407328221</v>
       </c>
       <c r="C23" t="n">
-        <v>0.5799008127365481</v>
+        <v>0.6618298626895199</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9998195883751866</v>
+        <v>0.9999999999997585</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9879226224243837</v>
+        <v>0.9999999999997243</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9965144841122164</v>
+        <v>0.9999999999998143</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0006091022674965992</v>
+        <v>0.0001100966324200179</v>
       </c>
       <c r="H23" t="n">
-        <v>0.2493890248995578</v>
+        <v>0.2007524016967964</v>
       </c>
       <c r="I23" t="n">
-        <v>3.887152786903103e-05</v>
+        <v>1.089072256656613e-13</v>
       </c>
       <c r="J23" t="n">
-        <v>0.001902406685654439</v>
+        <v>1.135344139075531e-13</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0009706392138215777</v>
+        <v>1.441145369649501e-13</v>
       </c>
       <c r="L23" t="n">
-        <v>0.00882274064944712</v>
+        <v>0.002101715004940108</v>
       </c>
       <c r="M23" t="n">
-        <v>0.02467999731557115</v>
+        <v>0.01049269424028061</v>
       </c>
       <c r="N23" t="n">
-        <v>1.000403688267089</v>
+        <v>1.000072967580529</v>
       </c>
       <c r="O23" t="n">
-        <v>0.02573067589593248</v>
+        <v>0.01093938995696077</v>
       </c>
       <c r="P23" t="n">
-        <v>184.8070487548574</v>
+        <v>188.2283042025219</v>
       </c>
       <c r="Q23" t="n">
-        <v>288.4114938686545</v>
+        <v>291.8327493163189</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>model_9_8_2</t>
+          <t>model_9_8_1</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9988570360365346</v>
+        <v>0.9998145407328221</v>
       </c>
       <c r="C24" t="n">
-        <v>0.5794765327169142</v>
+        <v>0.6618298626895199</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9998873617836003</v>
+        <v>0.9999999999997585</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9878664205124519</v>
+        <v>0.9999999999997243</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9965248086247368</v>
+        <v>0.9999999999998143</v>
       </c>
       <c r="G24" t="n">
-        <v>0.000678512782185456</v>
+        <v>0.0001100966324200179</v>
       </c>
       <c r="H24" t="n">
-        <v>0.249640895847155</v>
+        <v>0.2007524016967964</v>
       </c>
       <c r="I24" t="n">
-        <v>2.426905457134089e-05</v>
+        <v>1.089072256656613e-13</v>
       </c>
       <c r="J24" t="n">
-        <v>0.001911259509236068</v>
+        <v>1.135344139075531e-13</v>
       </c>
       <c r="K24" t="n">
-        <v>0.0009677640650520553</v>
+        <v>1.441145369649501e-13</v>
       </c>
       <c r="L24" t="n">
-        <v>0.009379098733719858</v>
+        <v>0.002101715004940108</v>
       </c>
       <c r="M24" t="n">
-        <v>0.02604827791208962</v>
+        <v>0.01049269424028061</v>
       </c>
       <c r="N24" t="n">
-        <v>1.000449690739724</v>
+        <v>1.000072967580529</v>
       </c>
       <c r="O24" t="n">
-        <v>0.02715720703017605</v>
+        <v>0.01093938995696077</v>
       </c>
       <c r="P24" t="n">
-        <v>184.5912144799578</v>
+        <v>188.2283042025219</v>
       </c>
       <c r="Q24" t="n">
-        <v>288.1956595937548</v>
+        <v>291.8327493163189</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>model_9_8_1</t>
+          <t>model_9_8_11</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.9987109276098587</v>
+        <v>0.9998145407328221</v>
       </c>
       <c r="C25" t="n">
-        <v>0.5790058151033133</v>
+        <v>0.6618298626895199</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9999431930920976</v>
+        <v>0.9999999999997585</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9877976625992128</v>
+        <v>0.9999999999997243</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9965269604886406</v>
+        <v>0.9999999999998143</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0007652490558156909</v>
+        <v>0.0001100966324200179</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2499203341565307</v>
+        <v>0.2007524016967964</v>
       </c>
       <c r="I25" t="n">
-        <v>1.223962871554779e-05</v>
+        <v>1.089072256656613e-13</v>
       </c>
       <c r="J25" t="n">
-        <v>0.001922090131448443</v>
+        <v>1.135344139075531e-13</v>
       </c>
       <c r="K25" t="n">
-        <v>0.0009671648184684662</v>
+        <v>1.441145369649501e-13</v>
       </c>
       <c r="L25" t="n">
-        <v>0.009999551132599833</v>
+        <v>0.002101715004940108</v>
       </c>
       <c r="M25" t="n">
-        <v>0.02766313532150127</v>
+        <v>0.01049269424028061</v>
       </c>
       <c r="N25" t="n">
-        <v>1.000507176022351</v>
+        <v>1.000072967580529</v>
       </c>
       <c r="O25" t="n">
-        <v>0.02884081226272203</v>
+        <v>0.01093938995696077</v>
       </c>
       <c r="P25" t="n">
-        <v>184.3506184279283</v>
+        <v>188.2283042025219</v>
       </c>
       <c r="Q25" t="n">
-        <v>287.9550635417254</v>
+        <v>291.8327493163189</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>model_9_8_0</t>
+          <t>model_9_8_24</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.998528706093992</v>
+        <v>0.9998145407328221</v>
       </c>
       <c r="C26" t="n">
-        <v>0.5784878105419293</v>
+        <v>0.6618298626895199</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9999823582028213</v>
+        <v>0.9999999999997585</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9877150240659114</v>
+        <v>0.9999999999997243</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9965187390408176</v>
+        <v>0.9999999999998143</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0008734236191937459</v>
+        <v>0.0001100966324200179</v>
       </c>
       <c r="H26" t="n">
-        <v>0.2502278440408001</v>
+        <v>0.2007524016967964</v>
       </c>
       <c r="I26" t="n">
-        <v>3.801105452053836e-06</v>
+        <v>1.089072256656613e-13</v>
       </c>
       <c r="J26" t="n">
-        <v>0.001935107203843586</v>
+        <v>1.135344139075531e-13</v>
       </c>
       <c r="K26" t="n">
-        <v>0.0009694543101558734</v>
+        <v>1.441145369649501e-13</v>
       </c>
       <c r="L26" t="n">
-        <v>0.01069179219767298</v>
+        <v>0.002101715004940108</v>
       </c>
       <c r="M26" t="n">
-        <v>0.02955374120468923</v>
+        <v>0.01049269424028061</v>
       </c>
       <c r="N26" t="n">
-        <v>1.000578869733511</v>
+        <v>1.000072967580529</v>
       </c>
       <c r="O26" t="n">
-        <v>0.030811905152451</v>
+        <v>0.01093938995696077</v>
       </c>
       <c r="P26" t="n">
-        <v>184.0861797489289</v>
+        <v>188.2283042025219</v>
       </c>
       <c r="Q26" t="n">
-        <v>287.690624862726</v>
+        <v>291.8327493163189</v>
       </c>
     </row>
   </sheetData>
